--- a/results/tables/compare/f_score_ablation_comparison_bold.xlsx
+++ b/results/tables/compare/f_score_ablation_comparison_bold.xlsx
@@ -8,19 +8,33 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://campusfl-my.sharepoint.com/personal/mahsa_choopannezhad_uni_li/Documents/Desktop/PhD materials/codes/Lifecycles-Processes/results/tables/compare/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{EDCFD9A8-D878-4E6B-8292-9B2D995B0652}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="30" documentId="8_{EDCFD9A8-D878-4E6B-8292-9B2D995B0652}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1AE56080-7AD9-4F2C-9574-876FA93082E4}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{E6BD246C-DCBC-4E41-91F2-E6B79A2CE303}"/>
   </bookViews>
   <sheets>
     <sheet name="f_score_ablation_comparison" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="18">
   <si>
     <t>discovery_method</t>
   </si>
@@ -62,12 +76,27 @@
   </si>
   <si>
     <t>heuristics_dep_0.5</t>
+  </si>
+  <si>
+    <t>a</t>
+  </si>
+  <si>
+    <t>b</t>
+  </si>
+  <si>
+    <t>c</t>
+  </si>
+  <si>
+    <t>b, c</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
+    <numFmt numFmtId="168" formatCode="0.000"/>
+  </numFmts>
   <fonts count="18" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -545,9 +574,13 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="168" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="2" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -960,19 +993,19 @@
       <c r="B2" t="s">
         <v>8</v>
       </c>
-      <c r="C2">
+      <c r="C2" s="4">
         <v>0.612253580301649</v>
       </c>
-      <c r="D2">
+      <c r="D2" s="4">
         <v>0.67939111316248801</v>
       </c>
-      <c r="E2">
+      <c r="E2" s="4">
         <v>0.30652030099613797</v>
       </c>
-      <c r="F2">
+      <c r="F2" s="4">
         <v>0.466745908911326</v>
       </c>
-      <c r="G2">
+      <c r="G2" s="4">
         <v>0.276562192508366</v>
       </c>
     </row>
@@ -983,19 +1016,19 @@
       <c r="B3" t="s">
         <v>9</v>
       </c>
-      <c r="C3">
+      <c r="C3" s="4">
         <v>0.53280752675975795</v>
       </c>
-      <c r="D3" s="1">
+      <c r="D3" s="5">
         <v>0.70858432422245499</v>
       </c>
-      <c r="E3" s="1">
+      <c r="E3" s="5">
         <v>0.392996038534627</v>
       </c>
-      <c r="F3" s="1">
+      <c r="F3" s="5">
         <v>0.51342182108534096</v>
       </c>
-      <c r="G3">
+      <c r="G3" s="4">
         <v>0.26249143961906102</v>
       </c>
     </row>
@@ -1006,19 +1039,19 @@
       <c r="B4" t="s">
         <v>10</v>
       </c>
-      <c r="C4">
+      <c r="C4" s="4">
         <v>0.52476729653751697</v>
       </c>
-      <c r="D4">
+      <c r="D4" s="4">
         <v>0.61837247697717901</v>
       </c>
-      <c r="E4" s="1">
+      <c r="E4" s="5">
         <v>0.62770900749303904</v>
       </c>
-      <c r="F4" s="1">
+      <c r="F4" s="5">
         <v>0.47589840652960103</v>
       </c>
-      <c r="G4" s="1">
+      <c r="G4" s="5">
         <v>0.33343966449176299</v>
       </c>
     </row>
@@ -1029,19 +1062,19 @@
       <c r="B5" t="s">
         <v>11</v>
       </c>
-      <c r="C5">
+      <c r="C5" s="4">
         <v>0.48454808275306099</v>
       </c>
-      <c r="D5">
+      <c r="D5" s="4">
         <v>0.66137187566628297</v>
       </c>
-      <c r="E5" s="1">
+      <c r="E5" s="5">
         <v>0.49422477443098201</v>
       </c>
-      <c r="F5" s="1">
+      <c r="F5" s="5">
         <v>0.50269659940070199</v>
       </c>
-      <c r="G5" s="1">
+      <c r="G5" s="5">
         <v>0.284136099260825</v>
       </c>
     </row>
@@ -1052,19 +1085,19 @@
       <c r="B6" t="s">
         <v>8</v>
       </c>
-      <c r="C6">
+      <c r="C6" s="4">
         <v>0.53110648180192599</v>
       </c>
-      <c r="D6">
+      <c r="D6" s="4">
         <v>0.38700405857306602</v>
       </c>
-      <c r="E6">
+      <c r="E6" s="4">
         <v>0.57542110202701602</v>
       </c>
-      <c r="F6">
+      <c r="F6" s="4">
         <v>0.63771275866034804</v>
       </c>
-      <c r="G6">
+      <c r="G6" s="4">
         <v>0.40108605850372098</v>
       </c>
     </row>
@@ -1075,19 +1108,19 @@
       <c r="B7" t="s">
         <v>9</v>
       </c>
-      <c r="C7" s="1">
+      <c r="C7" s="5">
         <v>0.53283581153885096</v>
       </c>
-      <c r="D7" s="1">
+      <c r="D7" s="5">
         <v>0.41856909533778902</v>
       </c>
-      <c r="E7" s="1">
+      <c r="E7" s="5">
         <v>0.65660403592439798</v>
       </c>
-      <c r="F7">
+      <c r="F7" s="4">
         <v>0.55506500946187698</v>
       </c>
-      <c r="G7" s="1">
+      <c r="G7" s="5">
         <v>0.47436218773696498</v>
       </c>
     </row>
@@ -1098,19 +1131,19 @@
       <c r="B8" t="s">
         <v>10</v>
       </c>
-      <c r="C8" s="1">
+      <c r="C8" s="5">
         <v>0.55059219176896201</v>
       </c>
-      <c r="D8" s="1">
+      <c r="D8" s="5">
         <v>0.38756572668320299</v>
       </c>
-      <c r="E8" s="1">
+      <c r="E8" s="5">
         <v>0.65604871557259503</v>
       </c>
-      <c r="F8" s="1">
+      <c r="F8" s="5">
         <v>0.65109103317128103</v>
       </c>
-      <c r="G8" s="1">
+      <c r="G8" s="5">
         <v>0.51846337620624405</v>
       </c>
     </row>
@@ -1121,19 +1154,19 @@
       <c r="B9" t="s">
         <v>11</v>
       </c>
-      <c r="C9" s="1">
+      <c r="C9" s="5">
         <v>0.59338217803243698</v>
       </c>
-      <c r="D9" s="1">
+      <c r="D9" s="5">
         <v>0.45815262846251797</v>
       </c>
-      <c r="E9" s="1">
+      <c r="E9" s="5">
         <v>0.656622364630569</v>
       </c>
-      <c r="F9" s="1">
+      <c r="F9" s="5">
         <v>0.69317660642199996</v>
       </c>
-      <c r="G9" s="1">
+      <c r="G9" s="5">
         <v>0.610734971403602</v>
       </c>
     </row>
@@ -1144,19 +1177,19 @@
       <c r="B10" t="s">
         <v>8</v>
       </c>
-      <c r="C10">
+      <c r="C10" s="4">
         <v>0.51798080917088996</v>
       </c>
-      <c r="D10">
+      <c r="D10" s="4">
         <v>0.37906377488449799</v>
       </c>
-      <c r="E10">
+      <c r="E10" s="4">
         <v>0.388834924910409</v>
       </c>
-      <c r="F10">
+      <c r="F10" s="4">
         <v>0.44278599294626397</v>
       </c>
-      <c r="G10">
+      <c r="G10" s="4">
         <v>0.51389949488259501</v>
       </c>
     </row>
@@ -1167,19 +1200,19 @@
       <c r="B11" t="s">
         <v>9</v>
       </c>
-      <c r="C11" s="1">
+      <c r="C11" s="5">
         <v>0.51955781821951996</v>
       </c>
-      <c r="D11" s="1">
+      <c r="D11" s="5">
         <v>0.49318530723874499</v>
       </c>
-      <c r="E11" s="1">
+      <c r="E11" s="5">
         <v>0.555543021248877</v>
       </c>
-      <c r="F11" s="1">
+      <c r="F11" s="5">
         <v>0.45553595664670099</v>
       </c>
-      <c r="G11" s="1">
+      <c r="G11" s="5">
         <v>0.54479373372565099</v>
       </c>
     </row>
@@ -1190,19 +1223,19 @@
       <c r="B12" t="s">
         <v>10</v>
       </c>
-      <c r="C12" s="1">
+      <c r="C12" s="5">
         <v>0.54260468549250696</v>
       </c>
-      <c r="D12" s="1">
+      <c r="D12" s="5">
         <v>0.46669997566216098</v>
       </c>
-      <c r="E12" s="1">
+      <c r="E12" s="5">
         <v>0.55677891658527601</v>
       </c>
-      <c r="F12" s="1">
+      <c r="F12" s="5">
         <v>0.53660007445577995</v>
       </c>
-      <c r="G12" s="1">
+      <c r="G12" s="5">
         <v>0.59996246578839596</v>
       </c>
     </row>
@@ -1213,21 +1246,372 @@
       <c r="B13" t="s">
         <v>11</v>
       </c>
-      <c r="C13" s="1">
+      <c r="C13" s="5">
         <v>0.55309212385547502</v>
       </c>
-      <c r="D13" s="1">
+      <c r="D13" s="5">
         <v>0.48923025328714198</v>
       </c>
-      <c r="E13" s="1">
+      <c r="E13" s="5">
         <v>0.62513892018799</v>
       </c>
-      <c r="F13" s="1">
+      <c r="F13" s="5">
         <v>0.50491995414287905</v>
       </c>
-      <c r="G13" s="1">
+      <c r="G13" s="5">
         <v>0.59926002457934502</v>
       </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F284EDE5-6AAB-4C16-B3EC-AA3095D4299A}">
+  <dimension ref="A1:M13"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="23.90625" bestFit="1" customWidth="1"/>
+    <col min="3" max="7" width="9.36328125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1">
+        <v>1</v>
+      </c>
+      <c r="D1">
+        <v>2</v>
+      </c>
+      <c r="E1">
+        <v>3</v>
+      </c>
+      <c r="F1">
+        <v>4</v>
+      </c>
+      <c r="G1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C2" s="2">
+        <v>0.3061267901508245</v>
+      </c>
+      <c r="D2" s="2">
+        <v>0.33969555658124401</v>
+      </c>
+      <c r="E2" s="2">
+        <v>0.15326015049806899</v>
+      </c>
+      <c r="F2" s="2">
+        <v>0.233372954455663</v>
+      </c>
+      <c r="G2" s="2">
+        <v>0.138281096254183</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C3" s="2">
+        <v>0.26640376337987898</v>
+      </c>
+      <c r="D3" s="3">
+        <v>0.35429216211122749</v>
+      </c>
+      <c r="E3" s="3">
+        <v>0.1964980192673135</v>
+      </c>
+      <c r="F3" s="3">
+        <v>0.25671091054267048</v>
+      </c>
+      <c r="G3" s="2">
+        <v>0.13124571980953051</v>
+      </c>
+      <c r="J3" s="1"/>
+      <c r="K3" s="1"/>
+      <c r="L3" s="1"/>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>7</v>
+      </c>
+      <c r="B4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C4" s="2">
+        <v>0.26238364826875848</v>
+      </c>
+      <c r="D4" s="2">
+        <v>0.3091862384885895</v>
+      </c>
+      <c r="E4" s="3">
+        <v>0.31385450374651952</v>
+      </c>
+      <c r="F4" s="3">
+        <v>0.23794920326480051</v>
+      </c>
+      <c r="G4" s="3">
+        <v>0.16671983224588149</v>
+      </c>
+      <c r="K4" s="1"/>
+      <c r="L4" s="1"/>
+      <c r="M4" s="1"/>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>7</v>
+      </c>
+      <c r="B5" t="s">
+        <v>17</v>
+      </c>
+      <c r="C5" s="2">
+        <v>0.2422740413765305</v>
+      </c>
+      <c r="D5" s="2">
+        <v>0.33068593783314149</v>
+      </c>
+      <c r="E5" s="3">
+        <v>0.247112387215491</v>
+      </c>
+      <c r="F5" s="3">
+        <v>0.251348299700351</v>
+      </c>
+      <c r="G5" s="3">
+        <v>0.1420680496304125</v>
+      </c>
+      <c r="K5" s="1"/>
+      <c r="L5" s="1"/>
+      <c r="M5" s="1"/>
+    </row>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>12</v>
+      </c>
+      <c r="B6" t="s">
+        <v>14</v>
+      </c>
+      <c r="C6" s="2">
+        <v>0.26555324090096299</v>
+      </c>
+      <c r="D6" s="2">
+        <v>0.19350202928653301</v>
+      </c>
+      <c r="E6" s="2">
+        <v>0.28771055101350801</v>
+      </c>
+      <c r="F6" s="2">
+        <v>0.31885637933017402</v>
+      </c>
+      <c r="G6" s="2">
+        <v>0.20054302925186049</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>12</v>
+      </c>
+      <c r="B7" t="s">
+        <v>15</v>
+      </c>
+      <c r="C7" s="3">
+        <v>0.26641790576942548</v>
+      </c>
+      <c r="D7" s="3">
+        <v>0.20928454766889451</v>
+      </c>
+      <c r="E7" s="3">
+        <v>0.32830201796219899</v>
+      </c>
+      <c r="F7" s="2">
+        <v>0.27753250473093849</v>
+      </c>
+      <c r="G7" s="3">
+        <v>0.23718109386848249</v>
+      </c>
+      <c r="I7" s="1"/>
+      <c r="J7" s="1"/>
+      <c r="K7" s="1"/>
+      <c r="M7" s="1"/>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
+        <v>12</v>
+      </c>
+      <c r="B8" t="s">
+        <v>16</v>
+      </c>
+      <c r="C8" s="3">
+        <v>0.27529609588448101</v>
+      </c>
+      <c r="D8" s="3">
+        <v>0.1937828633416015</v>
+      </c>
+      <c r="E8" s="3">
+        <v>0.32802435778629752</v>
+      </c>
+      <c r="F8" s="3">
+        <v>0.32554551658564052</v>
+      </c>
+      <c r="G8" s="3">
+        <v>0.25923168810312203</v>
+      </c>
+      <c r="I8" s="1"/>
+      <c r="J8" s="1"/>
+      <c r="K8" s="1"/>
+      <c r="L8" s="1"/>
+      <c r="M8" s="1"/>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
+        <v>12</v>
+      </c>
+      <c r="B9" t="s">
+        <v>17</v>
+      </c>
+      <c r="C9" s="3">
+        <v>0.29669108901621849</v>
+      </c>
+      <c r="D9" s="3">
+        <v>0.22907631423125899</v>
+      </c>
+      <c r="E9" s="3">
+        <v>0.3283111823152845</v>
+      </c>
+      <c r="F9" s="3">
+        <v>0.34658830321099998</v>
+      </c>
+      <c r="G9" s="3">
+        <v>0.305367485701801</v>
+      </c>
+      <c r="I9" s="1"/>
+      <c r="J9" s="1"/>
+      <c r="K9" s="1"/>
+      <c r="L9" s="1"/>
+      <c r="M9" s="1"/>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A10" t="s">
+        <v>13</v>
+      </c>
+      <c r="B10" t="s">
+        <v>14</v>
+      </c>
+      <c r="C10" s="2">
+        <v>0.25899040458544498</v>
+      </c>
+      <c r="D10" s="2">
+        <v>0.189531887442249</v>
+      </c>
+      <c r="E10" s="2">
+        <v>0.1944174624552045</v>
+      </c>
+      <c r="F10" s="2">
+        <v>0.22139299647313199</v>
+      </c>
+      <c r="G10" s="2">
+        <v>0.2569497474412975</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A11" t="s">
+        <v>13</v>
+      </c>
+      <c r="B11" t="s">
+        <v>15</v>
+      </c>
+      <c r="C11" s="3">
+        <v>0.25977890910975998</v>
+      </c>
+      <c r="D11" s="3">
+        <v>0.24659265361937249</v>
+      </c>
+      <c r="E11" s="3">
+        <v>0.2777715106244385</v>
+      </c>
+      <c r="F11" s="3">
+        <v>0.2277679783233505</v>
+      </c>
+      <c r="G11" s="3">
+        <v>0.27239686686282549</v>
+      </c>
+      <c r="I11" s="1"/>
+      <c r="J11" s="1"/>
+      <c r="K11" s="1"/>
+      <c r="L11" s="1"/>
+      <c r="M11" s="1"/>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A12" t="s">
+        <v>13</v>
+      </c>
+      <c r="B12" t="s">
+        <v>16</v>
+      </c>
+      <c r="C12" s="3">
+        <v>0.27130234274625348</v>
+      </c>
+      <c r="D12" s="3">
+        <v>0.23334998783108049</v>
+      </c>
+      <c r="E12" s="3">
+        <v>0.278389458292638</v>
+      </c>
+      <c r="F12" s="3">
+        <v>0.26830003722788998</v>
+      </c>
+      <c r="G12" s="3">
+        <v>0.29998123289419798</v>
+      </c>
+      <c r="I12" s="1"/>
+      <c r="J12" s="1"/>
+      <c r="K12" s="1"/>
+      <c r="L12" s="1"/>
+      <c r="M12" s="1"/>
+    </row>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A13" t="s">
+        <v>13</v>
+      </c>
+      <c r="B13" t="s">
+        <v>17</v>
+      </c>
+      <c r="C13" s="3">
+        <v>0.27654606192773751</v>
+      </c>
+      <c r="D13" s="3">
+        <v>0.24461512664357099</v>
+      </c>
+      <c r="E13" s="3">
+        <v>0.312569460093995</v>
+      </c>
+      <c r="F13" s="3">
+        <v>0.25245997707143952</v>
+      </c>
+      <c r="G13" s="3">
+        <v>0.29963001228967251</v>
+      </c>
+      <c r="I13" s="1"/>
+      <c r="J13" s="1"/>
+      <c r="K13" s="1"/>
+      <c r="L13" s="1"/>
+      <c r="M13" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
